--- a/rep.xlsx
+++ b/rep.xlsx
@@ -1884,15 +1884,15 @@
     <row r="2">
       <c r="A2" s="5" t="str">
         <f t="shared" ref="A2:A202" si="1">getJapanesePrefectureDirect(G2)</f>
-        <v>鳥取県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B2" s="6" t="str">
         <f t="shared" ref="B2:B202" si="2">getJapaneseCityWardDirect(G2)</f>
-        <v>鳥取市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C2" s="6" t="str">
         <f t="shared" ref="C2:C202" si="3">getJapaneseRemainingAddressDirect(G2)</f>
-        <v>東品治町102 鳥取ワシントンホテルプラザ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>5</v>
@@ -1917,15 +1917,15 @@
     <row r="3">
       <c r="A3" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>福岡県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B3" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>筑紫野市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C3" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>湯町1-14-3 アイビーホテル筑紫野</v>
+        <v>#NAME?</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>10</v>
@@ -1950,15 +1950,15 @@
     <row r="4">
       <c r="A4" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B4" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>豊橋市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C4" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>藤沢町141 ロワジールホテル豊橋</v>
+        <v>#NAME?</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>15</v>
@@ -1983,15 +1983,15 @@
     <row r="5">
       <c r="A5" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>奈良県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B5" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>奈良市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C5" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>三条本町4-21 スマイルホテル奈良</v>
+        <v>#NAME?</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>18</v>
@@ -2016,15 +2016,15 @@
     <row r="6">
       <c r="A6" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>岐阜県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B6" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>岐阜市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C6" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>神田町7-7-4 岐阜ワシントンホテルプラザ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>21</v>
@@ -2049,15 +2049,15 @@
     <row r="7">
       <c r="A7" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>岩手県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B7" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>北上市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C7" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>川岸1-14-1 ホテルシティプラザ北上</v>
+        <v>#NAME?</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>24</v>
@@ -2082,15 +2082,15 @@
     <row r="8">
       <c r="A8" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B8" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>神奈川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C8" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>東神奈川1-14-35 サンハロー東神奈川駅前</v>
+        <v>#NAME?</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -2121,15 +2121,15 @@
     <row r="9">
       <c r="A9" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B9" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>神奈川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C9" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>二ツ谷町2-10 餃子やと同じ建物の</v>
+        <v>#NAME?</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>37</v>
@@ -2160,15 +2160,15 @@
     <row r="10">
       <c r="A10" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B10" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>大和市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C10" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>中央林間4-1-5 メゾンラフィッテ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>43</v>
@@ -2197,15 +2197,15 @@
     <row r="11">
       <c r="A11" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B11" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>戸塚区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C11" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上倉田町1000 ハイツ山重</v>
+        <v>#NAME?</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>46</v>
@@ -2236,15 +2236,15 @@
     <row r="12">
       <c r="A12" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B12" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>横須賀市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C12" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>日の出町1-2-7 ノイエヨコスカ1番館</v>
+        <v>#NAME?</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>50</v>
@@ -2275,15 +2275,15 @@
     <row r="13">
       <c r="A13" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B13" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>藤沢市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C13" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>鵠沼花沢町2-2 グレースコート湘南</v>
+        <v>#NAME?</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>55</v>
@@ -2310,15 +2310,15 @@
     <row r="14">
       <c r="A14" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B14" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>藤沢市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C14" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>藤沢1031-1 日神パレステージ藤沢</v>
+        <v>#NAME?</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>58</v>
@@ -2345,15 +2345,15 @@
     <row r="15">
       <c r="A15" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B15" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>海老名市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C15" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>中新田3-5-23 シルフィード厚木</v>
+        <v>#NAME?</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>62</v>
@@ -2384,15 +2384,15 @@
     <row r="16">
       <c r="A16" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B16" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>茅ヶ崎市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C16" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>新栄町13-16 茅ヶ崎ダイカンプラザシティ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>67</v>
@@ -2423,15 +2423,15 @@
     <row r="17">
       <c r="A17" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>神奈川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B17" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>海老名市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C17" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>国分南1丁目11-6 フレクション海老名国分</v>
+        <v>#NAME?</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>71</v>
@@ -2458,15 +2458,15 @@
     <row r="18">
       <c r="A18" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B18" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>江東区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C18" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>亀戸6-12-7 第2伸光マンション</v>
+        <v>#NAME?</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>74</v>
@@ -2493,15 +2493,15 @@
     <row r="19">
       <c r="A19" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B19" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>江戸川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C19" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>西小岩1丁目30-11 ハイホーム沖田</v>
+        <v>#NAME?</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>78</v>
@@ -2532,15 +2532,15 @@
     <row r="20">
       <c r="A20" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B20" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>足立区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C20" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>綾瀬3-9-7 VERXEED綾瀬駅前</v>
+        <v>#NAME?</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>82</v>
@@ -2567,15 +2567,15 @@
     <row r="21">
       <c r="A21" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B21" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>足立区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C21" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>青井2丁目24-5 コートアオイ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>85</v>
@@ -2604,15 +2604,15 @@
     <row r="22">
       <c r="A22" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B22" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>墨田区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C22" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>錦糸1-6-9 メインステージ錦糸町駅前</v>
+        <v>#NAME?</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>89</v>
@@ -2643,15 +2643,15 @@
     <row r="23">
       <c r="A23" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B23" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>豊島区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C23" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>池袋本町1丁目34-5 北池ハイツ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>93</v>
@@ -2680,15 +2680,15 @@
     <row r="24">
       <c r="A24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B24" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>豊島区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>駒込2-4-2ペニンシュラ・コマゴメ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>97</v>
@@ -2715,15 +2715,15 @@
     <row r="25">
       <c r="A25" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B25" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>板橋区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C25" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>板橋1丁目50-7 グランヴァンXEBEC板橋</v>
+        <v>#NAME?</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>102</v>
@@ -2752,15 +2752,15 @@
     <row r="26">
       <c r="A26" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B26" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>大田区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C26" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>西蒲田7-29-5 ニューカマタビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>105</v>
@@ -2791,15 +2791,15 @@
     <row r="27">
       <c r="A27" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B27" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>大田区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C27" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>西蒲田7-7-1 グレイス蒲田</v>
+        <v>#NAME?</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>109</v>
@@ -2830,15 +2830,15 @@
     <row r="28">
       <c r="A28" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B28" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>千代田区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C28" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>神田小川町1丁目6-2 古室ビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>113</v>
@@ -2867,15 +2867,15 @@
     <row r="29">
       <c r="A29" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B29" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>杉並区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C29" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上荻1-15-13 柴ビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>117</v>
@@ -2904,15 +2904,15 @@
     <row r="30">
       <c r="A30" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B30" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>杉並区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C30" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上荻1丁目11-5 ロゼリウス荻窪</v>
+        <v>#NAME?</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>120</v>
@@ -2943,15 +2943,15 @@
     <row r="31">
       <c r="A31" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B31" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>渋谷区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C31" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>笹塚2丁目14-15 ウェルト笹塚ツイン1</v>
+        <v>#NAME?</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>123</v>
@@ -2980,15 +2980,15 @@
     <row r="32">
       <c r="A32" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B32" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>渋谷区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C32" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>宇田川町36-2 ノア渋谷</v>
+        <v>#NAME?</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>126</v>
@@ -3019,15 +3019,15 @@
     <row r="33">
       <c r="A33" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B33" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>世田谷区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C33" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>野沢2丁目34-5 Aden駒沢大学</v>
+        <v>#NAME?</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>131</v>
@@ -3056,15 +3056,15 @@
     <row r="34">
       <c r="A34" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B34" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>立川市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C34" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>曙町1丁目36-9 多摩セントラルビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>134</v>
@@ -3093,15 +3093,15 @@
     <row r="35">
       <c r="A35" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B35" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>立川市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C35" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>錦町1-5-25 コーポあきば</v>
+        <v>#NAME?</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>137</v>
@@ -3132,15 +3132,15 @@
     <row r="36">
       <c r="A36" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B36" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>府中市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C36" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>府中町2-5-7 ステーションビューロアール府中</v>
+        <v>#NAME?</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>141</v>
@@ -3169,15 +3169,15 @@
     <row r="37">
       <c r="A37" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B37" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>町田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C37" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>原町田6-16-7 アーバイルトルム町田</v>
+        <v>#NAME?</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>144</v>
@@ -3208,15 +3208,15 @@
     <row r="38">
       <c r="A38" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B38" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>町田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C38" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>原町田6丁目16-7 アーバイルトルム町田</v>
+        <v>#NAME?</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>148</v>
@@ -3247,15 +3247,15 @@
     <row r="39">
       <c r="A39" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B39" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>町田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C39" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>原町田6-26-3 ジョイフル町田</v>
+        <v>#NAME?</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>151</v>
@@ -3286,15 +3286,15 @@
     <row r="40">
       <c r="A40" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B40" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>東村</v>
+        <v>#NAME?</v>
       </c>
       <c r="C40" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>山市栄町2-2-10 Tokio久米川タワー</v>
+        <v>#NAME?</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>154</v>
@@ -3325,15 +3325,15 @@
     <row r="41">
       <c r="A41" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B41" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>武蔵野市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C41" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>吉祥寺本町2-24-6 吉祥寺グリーンハイツ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>157</v>
@@ -3360,15 +3360,15 @@
     <row r="42">
       <c r="A42" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B42" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>小金井市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C42" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>東町1-40-11 ロイヤルハイツハシモト</v>
+        <v>#NAME?</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>160</v>
@@ -3399,15 +3399,15 @@
     <row r="43">
       <c r="A43" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>東京都</v>
+        <v>#NAME?</v>
       </c>
       <c r="B43" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>西東京市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C43" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>田無町2丁目12-11 ハイツベルスプリング</v>
+        <v>#NAME?</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>164</v>
@@ -3436,15 +3436,15 @@
     <row r="44">
       <c r="A44" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B44" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>柏市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C44" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>柏6-2-7 コートヤード・シブヤ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>167</v>
@@ -3473,15 +3473,15 @@
     <row r="45">
       <c r="A45" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B45" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>柏市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C45" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>根戸1914-12 エソール・柏</v>
+        <v>#NAME?</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>170</v>
@@ -3510,15 +3510,15 @@
     <row r="46">
       <c r="A46" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B46" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中央区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C46" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>新宿2-14-16 パ―クプラザ千葉新宿</v>
+        <v>#NAME?</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>173</v>
@@ -3549,15 +3549,15 @@
     <row r="47">
       <c r="A47" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B47" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中央区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C47" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>南町2-18-16 カリンビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>177</v>
@@ -3586,15 +3586,15 @@
     <row r="48">
       <c r="A48" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B48" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>船橋市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C48" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>印内町612 プルミエール西船</v>
+        <v>#NAME?</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>181</v>
@@ -3625,15 +3625,15 @@
     <row r="49">
       <c r="A49" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B49" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>船橋市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C49" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>印内町570-1 鎌倉ビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>184</v>
@@ -3662,15 +3662,15 @@
     <row r="50">
       <c r="A50" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B50" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>船橋市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C50" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>本町6-9-6 ラプラビ船橋</v>
+        <v>#NAME?</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>188</v>
@@ -3697,15 +3697,15 @@
     <row r="51">
       <c r="A51" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B51" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>船橋市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C51" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>本町6-3-10 グリーンシティーときた</v>
+        <v>#NAME?</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>193</v>
@@ -3730,15 +3730,15 @@
     <row r="52">
       <c r="A52" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B52" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>習志野市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C52" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>谷津7丁目7-22 スーペリア津田沼</v>
+        <v>#NAME?</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>196</v>
@@ -3769,15 +3769,15 @@
     <row r="53">
       <c r="A53" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B53" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>八千代市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C53" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>勝田台1丁目30 京成サンコーポ勝田台C棟 3番階段</v>
+        <v>#NAME?</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>199</v>
@@ -3804,15 +3804,15 @@
     <row r="54">
       <c r="A54" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B54" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>八千代市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C54" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>勝田台北1-19-43 玄気道ビル第七</v>
+        <v>#NAME?</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>202</v>
@@ -3843,15 +3843,15 @@
     <row r="55">
       <c r="A55" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B55" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>八千代市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C55" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>勝田台1丁目30 京成サンコーポ勝田台C棟</v>
+        <v>#NAME?</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>206</v>
@@ -3880,15 +3880,15 @@
     <row r="56">
       <c r="A56" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B56" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>市川市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C56" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>南八幡4-4-20 市川ルーフガーデンハイツ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>209</v>
@@ -3919,15 +3919,15 @@
     <row r="57">
       <c r="A57" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B57" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>市川市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C57" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>行徳駅前2-7-1 遠藤ビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>212</v>
@@ -3958,15 +3958,15 @@
     <row r="58">
       <c r="A58" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>千葉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B58" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>佐倉市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C58" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>新町187-2 キャピタル一番館</v>
+        <v>#NAME?</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>216</v>
@@ -3995,15 +3995,15 @@
     <row r="59">
       <c r="A59" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B59" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>川越市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C59" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>稲荷町6-18 ブルーハイツK</v>
+        <v>#NAME?</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>220</v>
@@ -4032,15 +4032,15 @@
     <row r="60">
       <c r="A60" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B60" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>南区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C60" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>南本町2-14-18 第16ユーセードムス</v>
+        <v>#NAME?</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>224</v>
@@ -4069,15 +4069,15 @@
     <row r="61">
       <c r="A61" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B61" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>浦和区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C61" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>岸町4丁目26-8 プリムローズ岸町</v>
+        <v>#NAME?</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>227</v>
@@ -4106,15 +4106,15 @@
     <row r="62">
       <c r="A62" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B62" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>川口市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C62" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>芝新町4-14 ラフィスタ芝新町</v>
+        <v>#NAME?</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>232</v>
@@ -4143,15 +4143,15 @@
     <row r="63">
       <c r="A63" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B63" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>草加市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C63" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>谷塚町1363-1 リレント谷塚II</v>
+        <v>#NAME?</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>235</v>
@@ -4180,15 +4180,15 @@
     <row r="64">
       <c r="A64" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B64" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>草加市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C64" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>氷川町2149-19 ライブコート草加</v>
+        <v>#NAME?</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>238</v>
@@ -4215,15 +4215,15 @@
     <row r="65">
       <c r="A65" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B65" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>所沢市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C65" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>小手指町3-7-3 煉瓦館25</v>
+        <v>#NAME?</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>241</v>
@@ -4250,15 +4250,15 @@
     <row r="66">
       <c r="A66" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B66" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>飯能市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C66" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>柳町23-18 EXCEED飯能</v>
+        <v>#NAME?</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>244</v>
@@ -4289,15 +4289,15 @@
     <row r="67">
       <c r="A67" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B67" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>飯能市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C67" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>柳町9-14 グランシャリオ飯能</v>
+        <v>#NAME?</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>247</v>
@@ -4328,15 +4328,15 @@
     <row r="68">
       <c r="A68" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B68" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>ふじみ野市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C68" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上福岡1丁目7-10 ウィング上福岡</v>
+        <v>#NAME?</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>250</v>
@@ -4363,15 +4363,15 @@
     <row r="69">
       <c r="A69" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B69" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>ふじみ野市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C69" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上福岡1丁目13-4  麻雀クラブ方の階段から</v>
+        <v>#NAME?</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>253</v>
@@ -4398,15 +4398,15 @@
     <row r="70">
       <c r="A70" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B70" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>ふじみ野市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C70" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上福岡1丁目6-21 村田ビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>256</v>
@@ -4433,15 +4433,15 @@
     <row r="71">
       <c r="A71" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B71" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>熊谷市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C71" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>銀座1-153 ロハス星川</v>
+        <v>#NAME?</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>259</v>
@@ -4472,15 +4472,15 @@
     <row r="72">
       <c r="A72" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B72" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>大宮区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C72" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>桜木町2丁目457-1 志延舍</v>
+        <v>#NAME?</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>262</v>
@@ -4511,15 +4511,15 @@
     <row r="73">
       <c r="A73" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B73" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>狭山市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C73" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>新狭山2丁目23-11 オーク新狭山</v>
+        <v>#NAME?</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>265</v>
@@ -4550,15 +4550,15 @@
     <row r="74">
       <c r="A74" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B74" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>越谷市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C74" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>南越谷4丁目12-22 サクラビルディング</v>
+        <v>#NAME?</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>269</v>
@@ -4587,15 +4587,15 @@
     <row r="75">
       <c r="A75" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B75" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>朝霞市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C75" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>北原2丁目12-32  メゾンヨネダ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>272</v>
@@ -4624,15 +4624,15 @@
     <row r="76">
       <c r="A76" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>埼玉県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B76" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>朝霞市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C76" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>本町1丁目22-15 ウィンベルソロ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>276</v>
@@ -4661,15 +4661,15 @@
     <row r="77">
       <c r="A77" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B77" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>泉大津市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C77" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>東豊中町1-5-48 シンエイビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>279</v>
@@ -4700,15 +4700,15 @@
     <row r="78">
       <c r="A78" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B78" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>西成区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C78" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>旭1-8-5 サンハイツタケナワ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>282</v>
@@ -4737,15 +4737,15 @@
     <row r="79">
       <c r="A79" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B79" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>生野区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C79" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>鶴橋1-5-21 カーサフェリーチェ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>286</v>
@@ -4774,15 +4774,15 @@
     <row r="80">
       <c r="A80" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B80" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中央区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C80" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>備後町1-4-6  ラナップスクエ堺筋本町</v>
+        <v>#NAME?</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>289</v>
@@ -4811,15 +4811,15 @@
     <row r="81">
       <c r="A81" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B81" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中央区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C81" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>日本橋1丁目3-2 コージーアパートメント日本橋</v>
+        <v>#NAME?</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>292</v>
@@ -4850,15 +4850,15 @@
     <row r="82">
       <c r="A82" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B82" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中央区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C82" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>高津2丁目4-20 M.C.高津メゾンエルム</v>
+        <v>#NAME?</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>295</v>
@@ -4887,15 +4887,15 @@
     <row r="83">
       <c r="A83" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B83" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>天王寺区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C83" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>生玉町11-29</v>
+        <v>#NAME?</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>298</v>
@@ -4924,15 +4924,15 @@
     <row r="84">
       <c r="A84" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B84" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>淀川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C84" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>西中島1丁目14-4 プレサンス新大阪ストリーム</v>
+        <v>#NAME?</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>302</v>
@@ -4961,15 +4961,15 @@
     <row r="85">
       <c r="A85" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B85" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>淀川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C85" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>西中島5丁目8-21 マイルド新大阪レジデンス</v>
+        <v>#NAME?</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>305</v>
@@ -4998,15 +4998,15 @@
     <row r="86">
       <c r="A86" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B86" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>淀川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C86" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>西中島3-12-4 ATOLL西中島</v>
+        <v>#NAME?</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>310</v>
@@ -5035,15 +5035,15 @@
     <row r="87">
       <c r="A87" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪市</v>
+        <v>#NAME?</v>
       </c>
       <c r="B87" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>東淀川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C87" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>西淡路1-1-28 ライオンズマンション</v>
+        <v>#NAME?</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>313</v>
@@ -5072,15 +5072,15 @@
     <row r="88">
       <c r="A88" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B88" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>平野区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C88" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>背戸口5-6-12 カサ・エルドラード</v>
+        <v>#NAME?</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>316</v>
@@ -5111,15 +5111,15 @@
     <row r="89">
       <c r="A89" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B89" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>都島区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C89" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>東野田町4-14-10 レクシア京橋</v>
+        <v>#NAME?</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>320</v>
@@ -5148,15 +5148,15 @@
     <row r="90">
       <c r="A90" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B90" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>守口市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C90" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>寺内町1-5-5 クレイン守口</v>
+        <v>#NAME?</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>323</v>
@@ -5185,15 +5185,15 @@
     <row r="91">
       <c r="A91" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B91" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>守口市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C91" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>春日町1-19 アドヴァンテージ守口</v>
+        <v>#NAME?</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>326</v>
@@ -5218,15 +5218,15 @@
     <row r="92">
       <c r="A92" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B92" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>吹田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C92" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>江の木町17-16 アーデン江坂</v>
+        <v>#NAME?</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>329</v>
@@ -5253,15 +5253,15 @@
     <row r="93">
       <c r="A93" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>大阪府</v>
+        <v>#NAME?</v>
       </c>
       <c r="B93" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>松原市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C93" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上田1-4-8 ふぁみーゆ上田III</v>
+        <v>#NAME?</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>333</v>
@@ -5290,15 +5290,15 @@
     <row r="94">
       <c r="A94" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B94" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>名東区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C94" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>一社1-125 アサノビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>336</v>
@@ -5329,15 +5329,15 @@
     <row r="95">
       <c r="A95" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B95" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>名東区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C95" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>八前1-202 京和コーポ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>340</v>
@@ -5368,15 +5368,15 @@
     <row r="96">
       <c r="A96" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B96" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>南区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C96" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>柴田町3-22 ラディアント柴田</v>
+        <v>#NAME?</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>344</v>
@@ -5405,15 +5405,15 @@
     <row r="97">
       <c r="A97" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B97" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中川区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C97" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>高畑3-40 ブラザービル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>347</v>
@@ -5442,15 +5442,15 @@
     <row r="98">
       <c r="A98" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B98" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>北区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C98" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>若葉通1丁目21 メゾンコロル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>350</v>
@@ -5479,15 +5479,15 @@
     <row r="99">
       <c r="A99" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B99" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>西区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C99" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上小田井1-47 ブルーウェーブマンショ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>353</v>
@@ -5516,15 +5516,15 @@
     <row r="100">
       <c r="A100" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B100" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>港区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C100" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>名港1丁目1-19 三旺ポートタウン港</v>
+        <v>#NAME?</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>356</v>
@@ -5553,15 +5553,15 @@
     <row r="101">
       <c r="A101" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B101" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>春日井市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C101" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>八幡町35-1 ニューブラウンハイツ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>360</v>
@@ -5590,15 +5590,15 @@
     <row r="102">
       <c r="A102" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B102" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>小牧市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C102" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>小牧1-254 第2メゾンたけ宗</v>
+        <v>#NAME?</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>363</v>
@@ -5627,15 +5627,15 @@
     <row r="103">
       <c r="A103" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B103" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>豊橋市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C103" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>菰口町3-95 第5フクマルビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>366</v>
@@ -5664,15 +5664,15 @@
     <row r="104">
       <c r="A104" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B104" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>豊川市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C104" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>平尾町神田64-1 ル・ボア大黒平尾A</v>
+        <v>#NAME?</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>369</v>
@@ -5705,15 +5705,15 @@
     <row r="105">
       <c r="A105" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B105" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>半田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C105" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>乙川太田町2-87-2</v>
+        <v>#NAME?</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>374</v>
@@ -5742,15 +5742,15 @@
     <row r="106">
       <c r="A106" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B106" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>半田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C106" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>東郷町4-101-2 ウェルネスタウン</v>
+        <v>#NAME?</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>377</v>
@@ -5781,15 +5781,15 @@
     <row r="107">
       <c r="A107" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B107" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>大府市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C107" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>月見町1-28 ボンジュール大府</v>
+        <v>#NAME?</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>381</v>
@@ -5818,15 +5818,15 @@
     <row r="108">
       <c r="A108" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B108" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>あま市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C108" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>小橋方南山西154-2 小橋方コーポラスB棟</v>
+        <v>#NAME?</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>384</v>
@@ -5857,15 +5857,15 @@
     <row r="109">
       <c r="A109" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B109" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>尾張旭市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C109" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>瀬戸川町2-80 ロータスフラワー</v>
+        <v>#NAME?</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>388</v>
@@ -5896,15 +5896,15 @@
     <row r="110">
       <c r="A110" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B110" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>海部郡</v>
+        <v>#NAME?</v>
       </c>
       <c r="C110" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>蟹江町富吉4丁目139 近鉄富吉コーポB棟</v>
+        <v>#NAME?</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>392</v>
@@ -5935,15 +5935,15 @@
     <row r="111">
       <c r="A111" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B111" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>長久手市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C111" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>東狭間912 ガーデンハイツエクレール</v>
+        <v>#NAME?</v>
       </c>
       <c r="D111" s="7" t="s">
         <v>395</v>
@@ -5974,15 +5974,15 @@
     <row r="112">
       <c r="A112" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>愛知県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B112" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>瀬戸市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C112" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>瀬戸口町111 ブリード瀬戸口</v>
+        <v>#NAME?</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>399</v>
@@ -6013,15 +6013,15 @@
     <row r="113">
       <c r="A113" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>岐阜県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B113" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>瑞穂市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C113" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>野田新田4128-2 品川第2ビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>403</v>
@@ -6052,15 +6052,15 @@
     <row r="114">
       <c r="A114" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>岐阜県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B114" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>可児市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C114" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>広見6丁目40</v>
+        <v>#NAME?</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>406</v>
@@ -6091,15 +6091,15 @@
     <row r="115">
       <c r="A115" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>静岡県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B115" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中央区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C115" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>海老塚1-10-20</v>
+        <v>#NAME?</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>410</v>
@@ -6130,15 +6130,15 @@
     <row r="116">
       <c r="A116" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>静岡県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B116" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>袋井市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C116" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>高尾746-1 AAI高尾</v>
+        <v>#NAME?</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>413</v>
@@ -6169,15 +6169,15 @@
     <row r="117">
       <c r="A117" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>静岡県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B117" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>中央区</v>
+        <v>#NAME?</v>
       </c>
       <c r="C117" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>布橋1丁目17-40 城北パーソナルハイツW</v>
+        <v>#NAME?</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>416</v>
@@ -6208,15 +6208,15 @@
     <row r="118">
       <c r="A118" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>静岡県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B118" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>磐田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C118" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>森下700-11 シミズハイツ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>420</v>
@@ -6245,15 +6245,15 @@
     <row r="119">
       <c r="A119" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>静岡県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B119" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>掛川市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C119" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>杉谷2-6-12 BellWood</v>
+        <v>#NAME?</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>423</v>
@@ -6284,15 +6284,15 @@
     <row r="120">
       <c r="A120" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>静岡県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B120" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>沼津市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C120" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>高沢町9-8 パティオ高沢</v>
+        <v>#NAME?</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>427</v>
@@ -6323,15 +6323,15 @@
     <row r="121">
       <c r="A121" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>福島県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B121" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>郡山市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C121" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>安積荒井本町441 サンシヤインビル</v>
+        <v>#NAME?</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>431</v>
@@ -6362,15 +6362,15 @@
     <row r="122">
       <c r="A122" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>兵庫県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B122" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>西宮市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C122" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>深津町3-3 ダイドーメゾン西宮北口10</v>
+        <v>#NAME?</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>435</v>
@@ -6401,15 +6401,15 @@
     <row r="123">
       <c r="A123" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>兵庫県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B123" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>姫路市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C123" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>広畑区東新町1-38-1 デアリックス広畑</v>
+        <v>#NAME?</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>438</v>
@@ -6440,15 +6440,15 @@
     <row r="124">
       <c r="A124" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>兵庫県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B124" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>姫路市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C124" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>441</v>
@@ -6475,15 +6475,15 @@
     <row r="125">
       <c r="A125" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>長野県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B125" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>長野市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C125" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>大字長野東町132 アシスト長野マンション</v>
+        <v>#NAME?</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>444</v>
@@ -6512,15 +6512,15 @@
     <row r="126">
       <c r="A126" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>長野県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B126" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>松本市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C126" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>中央1丁目2-7 大東プラザニュー伊勢町</v>
+        <v>#NAME?</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>447</v>
@@ -6549,15 +6549,15 @@
     <row r="127">
       <c r="A127" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>長野県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B127" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>上田市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C127" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>上塩尻226-1 ザ・グレイス・シグマ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>450</v>
@@ -6588,15 +6588,15 @@
     <row r="128">
       <c r="A128" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>宮城県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B128" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>石巻市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C128" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>中央3丁目5-22 メゾン・ド・コパン</v>
+        <v>#NAME?</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>453</v>
@@ -6625,15 +6625,15 @@
     <row r="129">
       <c r="A129" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>石川県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B129" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>金沢市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C129" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>此花町3-3 ライブ1</v>
+        <v>#NAME?</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>456</v>
@@ -6662,15 +6662,15 @@
     <row r="130">
       <c r="A130" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>滋賀県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B130" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>大津市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C130" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>中央1丁目2-35 アセンティアびわこ</v>
+        <v>#NAME?</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>459</v>
@@ -6699,15 +6699,15 @@
     <row r="131">
       <c r="A131" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>徳島県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B131" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>徳島市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C131" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>銀座10 福助ビル第63</v>
+        <v>#NAME?</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>462</v>
@@ -6738,15 +6738,15 @@
     <row r="132">
       <c r="A132" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>青森県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B132" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>青森市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C132" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>安方1丁目9-16 エクセルビュー</v>
+        <v>#NAME?</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>465</v>
@@ -6775,15 +6775,15 @@
     <row r="133">
       <c r="A133" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>新潟県</v>
+        <v>#NAME?</v>
       </c>
       <c r="B133" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>長岡市</v>
+        <v>#NAME?</v>
       </c>
       <c r="C133" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>渡里町4-5 オクトワール長岡中央</v>
+        <v>#NAME?</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>468</v>
@@ -6814,15 +6814,15 @@
     <row r="134">
       <c r="A134" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B134" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C134" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D134" s="19"/>
       <c r="E134" s="19"/>
@@ -6837,15 +6837,15 @@
     <row r="135">
       <c r="A135" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B135" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C135" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D135" s="19"/>
       <c r="E135" s="19"/>
@@ -6860,15 +6860,15 @@
     <row r="136">
       <c r="A136" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B136" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C136" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D136" s="19"/>
       <c r="E136" s="19"/>
@@ -6883,15 +6883,15 @@
     <row r="137">
       <c r="A137" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B137" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C137" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D137" s="19"/>
       <c r="E137" s="19"/>
@@ -6906,15 +6906,15 @@
     <row r="138">
       <c r="A138" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B138" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C138" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D138" s="19"/>
       <c r="E138" s="19"/>
@@ -6929,15 +6929,15 @@
     <row r="139">
       <c r="A139" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B139" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C139" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D139" s="19"/>
       <c r="E139" s="19"/>
@@ -6952,15 +6952,15 @@
     <row r="140">
       <c r="A140" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B140" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C140" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D140" s="19"/>
       <c r="E140" s="19"/>
@@ -6975,15 +6975,15 @@
     <row r="141">
       <c r="A141" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B141" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C141" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D141" s="19"/>
       <c r="E141" s="19"/>
@@ -6998,15 +6998,15 @@
     <row r="142">
       <c r="A142" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B142" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C142" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D142" s="19"/>
       <c r="E142" s="19"/>
@@ -7021,15 +7021,15 @@
     <row r="143">
       <c r="A143" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B143" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C143" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D143" s="19"/>
       <c r="E143" s="19"/>
@@ -7044,15 +7044,15 @@
     <row r="144">
       <c r="A144" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B144" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C144" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D144" s="19"/>
       <c r="E144" s="19"/>
@@ -7067,15 +7067,15 @@
     <row r="145">
       <c r="A145" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B145" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C145" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D145" s="19"/>
       <c r="E145" s="19"/>
@@ -7090,15 +7090,15 @@
     <row r="146">
       <c r="A146" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B146" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C146" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D146" s="19"/>
       <c r="E146" s="19"/>
@@ -7113,15 +7113,15 @@
     <row r="147">
       <c r="A147" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B147" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C147" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D147" s="19"/>
       <c r="E147" s="19"/>
@@ -7136,15 +7136,15 @@
     <row r="148">
       <c r="A148" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B148" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C148" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D148" s="19"/>
       <c r="E148" s="19"/>
@@ -7159,15 +7159,15 @@
     <row r="149">
       <c r="A149" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B149" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C149" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D149" s="19"/>
       <c r="E149" s="19"/>
@@ -7182,15 +7182,15 @@
     <row r="150">
       <c r="A150" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B150" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C150" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D150" s="19"/>
       <c r="E150" s="19"/>
@@ -7205,15 +7205,15 @@
     <row r="151">
       <c r="A151" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B151" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C151" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D151" s="19"/>
       <c r="E151" s="19"/>
@@ -7228,15 +7228,15 @@
     <row r="152">
       <c r="A152" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B152" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C152" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D152" s="19"/>
       <c r="E152" s="19"/>
@@ -7251,15 +7251,15 @@
     <row r="153">
       <c r="A153" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B153" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C153" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D153" s="19"/>
       <c r="E153" s="19"/>
@@ -7274,15 +7274,15 @@
     <row r="154">
       <c r="A154" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B154" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C154" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D154" s="19"/>
       <c r="E154" s="19"/>
@@ -7297,15 +7297,15 @@
     <row r="155">
       <c r="A155" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B155" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C155" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D155" s="19"/>
       <c r="E155" s="19"/>
@@ -7320,15 +7320,15 @@
     <row r="156">
       <c r="A156" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B156" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C156" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D156" s="19"/>
       <c r="E156" s="19"/>
@@ -7343,15 +7343,15 @@
     <row r="157">
       <c r="A157" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B157" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C157" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D157" s="19"/>
       <c r="E157" s="19"/>
@@ -7366,15 +7366,15 @@
     <row r="158">
       <c r="A158" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B158" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C158" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D158" s="19"/>
       <c r="E158" s="19"/>
@@ -7389,15 +7389,15 @@
     <row r="159">
       <c r="A159" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C159" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D159" s="19"/>
       <c r="E159" s="19"/>
@@ -7412,15 +7412,15 @@
     <row r="160">
       <c r="A160" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B160" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C160" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D160" s="19"/>
       <c r="E160" s="19"/>
@@ -7435,15 +7435,15 @@
     <row r="161">
       <c r="A161" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B161" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C161" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D161" s="19"/>
       <c r="E161" s="19"/>
@@ -7458,15 +7458,15 @@
     <row r="162">
       <c r="A162" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B162" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C162" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D162" s="19"/>
       <c r="E162" s="19"/>
@@ -7481,15 +7481,15 @@
     <row r="163">
       <c r="A163" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B163" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C163" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D163" s="19"/>
       <c r="E163" s="19"/>
@@ -7504,15 +7504,15 @@
     <row r="164">
       <c r="A164" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B164" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C164" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D164" s="19"/>
       <c r="E164" s="19"/>
@@ -7527,15 +7527,15 @@
     <row r="165">
       <c r="A165" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B165" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C165" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D165" s="19"/>
       <c r="E165" s="19"/>
@@ -7550,15 +7550,15 @@
     <row r="166">
       <c r="A166" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B166" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C166" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D166" s="19"/>
       <c r="E166" s="19"/>
@@ -7573,15 +7573,15 @@
     <row r="167">
       <c r="A167" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B167" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C167" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D167" s="19"/>
       <c r="E167" s="19"/>
@@ -7596,15 +7596,15 @@
     <row r="168">
       <c r="A168" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B168" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C168" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D168" s="19"/>
       <c r="E168" s="19"/>
@@ -7619,15 +7619,15 @@
     <row r="169">
       <c r="A169" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B169" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C169" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D169" s="19"/>
       <c r="E169" s="19"/>
@@ -7642,15 +7642,15 @@
     <row r="170">
       <c r="A170" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B170" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C170" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D170" s="19"/>
       <c r="E170" s="19"/>
@@ -7665,15 +7665,15 @@
     <row r="171">
       <c r="A171" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B171" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C171" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D171" s="19"/>
       <c r="E171" s="19"/>
@@ -7688,15 +7688,15 @@
     <row r="172">
       <c r="A172" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B172" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C172" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D172" s="19"/>
       <c r="E172" s="19"/>
@@ -7711,15 +7711,15 @@
     <row r="173">
       <c r="A173" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B173" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C173" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D173" s="19"/>
       <c r="E173" s="19"/>
@@ -7734,15 +7734,15 @@
     <row r="174">
       <c r="A174" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B174" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C174" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D174" s="19"/>
       <c r="E174" s="19"/>
@@ -7757,15 +7757,15 @@
     <row r="175">
       <c r="A175" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B175" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C175" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D175" s="19"/>
       <c r="E175" s="19"/>
@@ -7780,15 +7780,15 @@
     <row r="176">
       <c r="A176" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B176" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C176" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D176" s="19"/>
       <c r="E176" s="19"/>
@@ -7803,15 +7803,15 @@
     <row r="177">
       <c r="A177" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B177" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C177" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D177" s="19"/>
       <c r="E177" s="19"/>
@@ -7826,15 +7826,15 @@
     <row r="178">
       <c r="A178" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B178" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C178" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D178" s="19"/>
       <c r="E178" s="19"/>
@@ -7849,15 +7849,15 @@
     <row r="179">
       <c r="A179" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C179" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D179" s="19"/>
       <c r="E179" s="19"/>
@@ -7872,15 +7872,15 @@
     <row r="180">
       <c r="A180" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B180" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C180" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D180" s="19"/>
       <c r="E180" s="19"/>
@@ -7895,15 +7895,15 @@
     <row r="181">
       <c r="A181" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B181" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C181" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D181" s="19"/>
       <c r="E181" s="19"/>
@@ -7918,15 +7918,15 @@
     <row r="182">
       <c r="A182" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B182" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C182" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D182" s="19"/>
       <c r="E182" s="19"/>
@@ -7941,15 +7941,15 @@
     <row r="183">
       <c r="A183" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B183" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C183" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D183" s="19"/>
       <c r="E183" s="19"/>
@@ -7964,15 +7964,15 @@
     <row r="184">
       <c r="A184" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B184" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C184" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D184" s="19"/>
       <c r="E184" s="19"/>
@@ -7987,15 +7987,15 @@
     <row r="185">
       <c r="A185" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B185" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C185" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D185" s="19"/>
       <c r="E185" s="19"/>
@@ -8010,15 +8010,15 @@
     <row r="186">
       <c r="A186" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B186" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C186" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D186" s="19"/>
       <c r="E186" s="19"/>
@@ -8033,15 +8033,15 @@
     <row r="187">
       <c r="A187" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B187" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C187" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D187" s="19"/>
       <c r="E187" s="19"/>
@@ -8056,15 +8056,15 @@
     <row r="188">
       <c r="A188" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B188" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C188" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D188" s="19"/>
       <c r="E188" s="19"/>
@@ -8079,15 +8079,15 @@
     <row r="189">
       <c r="A189" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B189" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C189" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D189" s="19"/>
       <c r="E189" s="19"/>
@@ -8102,15 +8102,15 @@
     <row r="190">
       <c r="A190" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B190" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C190" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D190" s="19"/>
       <c r="E190" s="19"/>
@@ -8125,15 +8125,15 @@
     <row r="191">
       <c r="A191" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B191" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C191" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D191" s="19"/>
       <c r="E191" s="19"/>
@@ -8148,15 +8148,15 @@
     <row r="192">
       <c r="A192" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B192" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C192" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D192" s="19"/>
       <c r="E192" s="19"/>
@@ -8171,15 +8171,15 @@
     <row r="193">
       <c r="A193" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B193" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C193" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D193" s="19"/>
       <c r="E193" s="19"/>
@@ -8194,15 +8194,15 @@
     <row r="194">
       <c r="A194" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B194" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C194" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D194" s="19"/>
       <c r="E194" s="19"/>
@@ -8217,15 +8217,15 @@
     <row r="195">
       <c r="A195" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B195" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C195" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D195" s="19"/>
       <c r="E195" s="19"/>
@@ -8240,15 +8240,15 @@
     <row r="196">
       <c r="A196" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B196" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C196" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D196" s="19"/>
       <c r="E196" s="19"/>
@@ -8263,15 +8263,15 @@
     <row r="197">
       <c r="A197" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B197" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C197" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D197" s="19"/>
       <c r="E197" s="19"/>
@@ -8286,15 +8286,15 @@
     <row r="198">
       <c r="A198" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B198" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C198" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D198" s="19"/>
       <c r="E198" s="22"/>
@@ -8309,15 +8309,15 @@
     <row r="199">
       <c r="A199" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B199" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C199" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D199" s="19"/>
       <c r="E199" s="22"/>
@@ -8332,15 +8332,15 @@
     <row r="200">
       <c r="A200" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B200" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C200" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D200" s="19"/>
       <c r="E200" s="22"/>
@@ -8355,15 +8355,15 @@
     <row r="201">
       <c r="A201" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B201" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C201" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D201" s="19"/>
       <c r="E201" s="22"/>
@@ -8378,15 +8378,15 @@
     <row r="202">
       <c r="A202" s="5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="B202" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="C202" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>#NAME?</v>
       </c>
       <c r="D202" s="19"/>
       <c r="E202" s="22"/>
@@ -17654,28 +17654,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="K228:L228"/>
+    <mergeCell ref="K237:L237"/>
     <mergeCell ref="K239:L239"/>
     <mergeCell ref="K240:L240"/>
     <mergeCell ref="K249:L249"/>
     <mergeCell ref="K253:L253"/>
     <mergeCell ref="K258:L258"/>
-    <mergeCell ref="K223:L223"/>
-    <mergeCell ref="K224:L224"/>
-    <mergeCell ref="K226:L226"/>
-    <mergeCell ref="K228:L228"/>
-    <mergeCell ref="K237:L237"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="K116:L116"/>
     <mergeCell ref="K198:L198"/>
     <mergeCell ref="K204:L204"/>
     <mergeCell ref="K210:L210"/>
     <mergeCell ref="K211:L211"/>
     <mergeCell ref="K222:L222"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="K223:L223"/>
+    <mergeCell ref="K224:L224"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/rep.xlsx
+++ b/rep.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="value_only_temp" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Trang tính1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
